--- a/web/public/forms/orig/o-dojang-gyehoekseo.xlsx
+++ b/web/public/forms/orig/o-dojang-gyehoekseo.xlsx
@@ -925,7 +925,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1053,7 +1053,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="N1" s="72" t="inlineStr">
@@ -2475,7 +2475,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="72" t="inlineStr">
@@ -3313,7 +3313,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="72" t="inlineStr">
@@ -5393,7 +5393,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="72" t="inlineStr">
@@ -7144,7 +7144,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="72" t="inlineStr">
@@ -8606,7 +8606,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -9235,7 +9235,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
@@ -10624,7 +10624,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -11345,7 +11345,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -13424,7 +13424,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -15036,7 +15036,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -16499,7 +16499,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="72" t="inlineStr">
@@ -16596,7 +16596,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="72" t="inlineStr">

--- a/web/public/forms/orig/o-dojang-gyehoekseo.xlsx
+++ b/web/public/forms/orig/o-dojang-gyehoekseo.xlsx
@@ -892,7 +892,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
@@ -2666,7 +2666,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3347,7 +3347,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -5426,7 +5426,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
